--- a/data/Data.xlsx
+++ b/data/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5eac33cd60952162/Documents/Airfoil CFD - Project 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="492" documentId="8_{C3D95630-B24A-4D77-97B0-50644558C45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84C22FB6-9D76-4E76-A965-A469BFBACE5E}"/>
+  <xr:revisionPtr revIDLastSave="493" documentId="8_{C3D95630-B24A-4D77-97B0-50644558C45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1805DDC8-EB65-4305-9CE5-80598394C9BC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57F4C7C6-6B1D-4D30-867C-826791EE220A}"/>
   </bookViews>
@@ -10941,15 +10941,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:colOff>251133</xdr:colOff>
       <xdr:row>109</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>43631</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1052700</xdr:colOff>
+      <xdr:colOff>1265733</xdr:colOff>
       <xdr:row>128</xdr:row>
-      <xdr:rowOff>144330</xdr:rowOff>
+      <xdr:rowOff>168911</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
